--- a/invoice_agent/willway_202608.xlsx
+++ b/invoice_agent/willway_202608.xlsx
@@ -478,7 +478,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MTG</t>
+          <t>MTG 他</t>
         </is>
       </c>
       <c r="D2" t="n">
